--- a/air_vehicle_design/sizing/temp_Casey/inputs/Mission_Profile.xlsx
+++ b/air_vehicle_design/sizing/temp_Casey/inputs/Mission_Profile.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\John Freeman\Desktop\Academics\VRMastersProgram\code\air-vehicle-design\examples\F-16A B Block 10 and 15\Operator\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\John Freeman\Desktop\Academics\VRMastersProgram\code\air-vehicle-design\air_vehicle_design\sizing\temp_Casey\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6522DA05-673C-4AA3-870C-54573F647B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F57DCF2-7E6D-4ECD-A29E-FF873B0A6767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="384" windowWidth="23256" windowHeight="12720" activeTab="1" xr2:uid="{5FD27DBB-5210-421F-BEEA-403866C08751}"/>
+    <workbookView xWindow="23340" yWindow="1200" windowWidth="21600" windowHeight="12552" activeTab="1" xr2:uid="{5FD27DBB-5210-421F-BEEA-403866C08751}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -367,74 +367,6 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -952,7 +884,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="5">
-        <v>0.87</v>
+        <v>0.28199999999999997</v>
       </c>
       <c r="G9" s="5">
         <v>0.87</v>
@@ -974,11 +906,10 @@
         <v>0.87</v>
       </c>
       <c r="L9" s="6">
+        <v>0.31</v>
+      </c>
+      <c r="M9" s="6">
         <v>0.3</v>
-      </c>
-      <c r="M9" s="6">
-        <f>0</f>
-        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">

--- a/air_vehicle_design/sizing/temp_Casey/inputs/Mission_Profile.xlsx
+++ b/air_vehicle_design/sizing/temp_Casey/inputs/Mission_Profile.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\John Freeman\Desktop\Academics\VRMastersProgram\code\air-vehicle-design\air_vehicle_design\sizing\temp_Casey\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F57DCF2-7E6D-4ECD-A29E-FF873B0A6767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DCD0D86-2134-404C-B9A9-C2103682C618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23340" yWindow="1200" windowWidth="21600" windowHeight="12552" activeTab="1" xr2:uid="{5FD27DBB-5210-421F-BEEA-403866C08751}"/>
+    <workbookView xWindow="-120" yWindow="330" windowWidth="29040" windowHeight="15990" activeTab="1" xr2:uid="{5FD27DBB-5210-421F-BEEA-403866C08751}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -1098,7 +1098,7 @@
         <v>24</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>24</v>
